--- a/Client/Configs/GameConfig/Datas/effect.xlsx
+++ b/Client/Configs/GameConfig/Datas/effect.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,21 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -133,76 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>效果ID。被 skill.xlsx 的 effectId 引用。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>效果类型。当前 Damage=造成伤害；后续可扩展 Heal/AddBuff/Knockback/Stun。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>效果数值。Damage 时表示伤害数值。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>数值类型。Flat=固定值；后续可扩展 AttackPercent/MaxHpPercent 等。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>关联Buff ID。0表示不附加Buff；非0时指向 buff.xlsx。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>效果持续时间，单位秒。瞬时伤害填0；持续效果可填持续秒数。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>范围半径，单位米。0表示单体；大于0可作为AOE半径。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>击退距离，单位米。0表示不击退。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>控制类型。None/Stun/Slow/Silence 等，当前原型先用 None。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>属性类型。None/Attack/MoveSpeed/CastSpeed 等，给属性修改类效果用。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>修改方式。None/Add/Percent/Mul 等，给属性修改类效果用。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>修改值。比如减速30%可以约定 modifierType=Percent，modifierValue=-0.3。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,289 +413,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valueType</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>buffId</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>knockbackDistance</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>controlType</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>statType</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>modifierType</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>modifierValue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>效果ID。被 skill.xlsx 的 effectId 引用。</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>效果类型。当前 Damage=造成伤害；后续可扩展 Heal/AddBuff/Knockback/Stun。</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>效果数值。Damage 时表示伤害数值。</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>数值类型。Flat=固定值；后续可扩展 AttackPercent/MaxHpPercent 等。</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>关联Buff ID。0表示不附加Buff；非0时指向 buff.xlsx。</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>效果持续时间，单位秒。瞬时伤害填0；持续效果可填持续秒数。</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>范围半径，单位米。0表示单体；大于0可作为AOE半径。</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>击退距离，单位米。0表示不击退。</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>控制类型。None/Stun/Slow/Silence 等，当前原型先用 None。</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>属性类型。None/Attack/MoveSpeed/CastSpeed 等，给属性修改类效果用。</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>修改方式。None/Add/Percent/Mul 等，给属性修改类效果用。</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>修改值。比如减速30%可以约定 modifierType=Percent，modifierValue=-0.3。</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Effect id.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Effect type.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Value.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Value type.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Buff id.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Duration.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Radius.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Knockback distance.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Control type.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Stat type.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Modifier type.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Modifier value.</t>
         </is>
       </c>
     </row>
@@ -834,50 +738,241 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>500101</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>200201</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>24</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>200202</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>500201</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>200301</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>200401</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>500400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Client/Configs/GameConfig/Datas/effect.xlsx
+++ b/Client/Configs/GameConfig/Datas/effect.xlsx
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-0.25</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7">

--- a/Client/Configs/GameConfig/Datas/effect.xlsx
+++ b/Client/Configs/GameConfig/Datas/effect.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,7 +686,7 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>200101</v>
+        <v>210101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -734,15 +734,15 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>200102</v>
+        <v>210102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AddBuff</t>
+          <t>GenerateResource</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>500101</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -763,26 +763,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MoveSpeed</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Percent</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>200201</v>
+        <v>210201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>200202</v>
+        <v>210202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>500201</v>
+        <v>500301</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -878,15 +878,15 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>200301</v>
+        <v>210301</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>AreaDamage</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>200401</v>
+        <v>210302</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>500400</v>
+        <v>500302</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -955,21 +955,501 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Slow</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>AttackSpeed</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>210303</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AddThreat</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>260</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>220101</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>220201</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>220202</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>500101</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>220301</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>220302</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>500201</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>230101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>230201</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>108</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>230301</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Resurrect</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MaxHpPercent</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>200400</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AddBuff</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>500400</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
